--- a/metrics_nsga2.xlsx
+++ b/metrics_nsga2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="5">
   <si>
     <t>HV</t>
   </si>
@@ -94,10 +94,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>1.0408555502090866</v>
+        <v>1.0565627045557013</v>
       </c>
       <c r="B2" s="0">
-        <v>0.024322842260971787</v>
+        <v>0.022001930129508327</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>3</v>
@@ -105,10 +105,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>1.0385098739422001</v>
+        <v>1.0916368165520778</v>
       </c>
       <c r="B3" s="0">
-        <v>0.025263963020218622</v>
+        <v>0.010373072898262111</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>3</v>
@@ -116,10 +116,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>1.0513886301722326</v>
+        <v>1.0934269341883522</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0032564033168042388</v>
+        <v>0.0057410306126089777</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>4</v>
@@ -127,10 +127,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>1.0502472034007728</v>
+        <v>1.095545330613823</v>
       </c>
       <c r="B5" s="0">
-        <v>0.0038409470757376062</v>
+        <v>0.0037391930694361509</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>4</v>

--- a/metrics_nsga2.xlsx
+++ b/metrics_nsga2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="77" uniqueCount="5">
   <si>
     <t>HV</t>
   </si>
@@ -76,7 +76,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="1" max="1" width="12.7109375" customWidth="true"/>
     <col min="2" max="2" width="14.7109375" customWidth="true"/>
     <col min="3" max="3" width="9.7109375" customWidth="true"/>
   </cols>
@@ -94,10 +94,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>1.0565627045557013</v>
+        <v>0.88988201873445216</v>
       </c>
       <c r="B2" s="0">
-        <v>0.022001930129508327</v>
+        <v>0.046198030093591989</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>3</v>
@@ -105,10 +105,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>1.0916368165520778</v>
+        <v>0.88858474051907221</v>
       </c>
       <c r="B3" s="0">
-        <v>0.010373072898262111</v>
+        <v>0.047594199234877586</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>3</v>
@@ -116,10 +116,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>1.0934269341883522</v>
+        <v>0.9577191942820511</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0057410306126089777</v>
+        <v>0.0026996113614312515</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>4</v>
@@ -127,10 +127,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>1.095545330613823</v>
+        <v>0.94701854179815448</v>
       </c>
       <c r="B5" s="0">
-        <v>0.0037391930694361509</v>
+        <v>0.0038599777458824761</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>4</v>
